--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,117 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122066207</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110011</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dalhem, 700 m VSV, Småvänderot, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>433382</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6204979</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2001-06-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2001-06-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Fuktig björkskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110011</v>
+        <v>110013</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,6 +989,11 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>Träne</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>M-Kri-2417</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110013</v>
+        <v>110020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110020</v>
+        <v>110029</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110055</v>
+        <v>110065</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110065</v>
+        <v>110078</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110078</v>
+        <v>110083</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110083</v>
+        <v>110092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,11 +940,6 @@
       </c>
       <c r="E4" t="n">
         <v>221049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Småvänderot</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64029637</v>
+        <v>122066207</v>
       </c>
       <c r="B3" t="n">
-        <v>107952</v>
+        <v>110092</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,11 +810,6 @@
       <c r="E3" t="n">
         <v>221049</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Småvänderot</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Valeriana dioica</t>
@@ -828,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>700m V-VSV Dalhem, Sk</t>
+          <t>Dalhem, 700 m VSV, Småvänderot, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433381.5851822785</v>
+        <v>433382</v>
       </c>
       <c r="R3" t="n">
-        <v>6204978.863592361</v>
+        <v>6204979</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,29 +855,19 @@
           <t>Träne</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M-Kri-2417</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2001-06-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2001-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Valeriana dioica/3D1g2931/Träne s:n/THm/ /Tord Holm,Hässleholm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,137 +881,21 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>fuktig björkskog</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SkFlora    661662</t>
+          <t>Fuktig björkskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Stefan Andersson</t>
+          <t>Via Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>122066207</v>
-      </c>
-      <c r="B4" t="n">
-        <v>110092</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221049</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Valeriana dioica</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Dalhem, 700 m VSV, Småvänderot, Sk</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>433382</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6204979</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Träne</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>M-Kri-2417</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2001-06-18</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2001-06-18</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Fuktig björkskog</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,131 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125139847</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109906</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dalhem, 700 m VSV, Småvänderot, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>433469</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6205005</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>M-Kri-2417</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>I björkdunge i betesmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>125139847</v>
       </c>
       <c r="B4" t="n">
-        <v>109906</v>
+        <v>110092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -906,12 +906,7 @@
         <v>125139847</v>
       </c>
       <c r="B4" t="n">
-        <v>110092</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110729</v>
+        <v>110732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110732</v>
+        <v>110819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110819</v>
+        <v>110822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110822</v>
+        <v>110848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110848</v>
+        <v>110849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110849</v>
+        <v>110850</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>34288</v>
       </c>
       <c r="B2" t="n">
-        <v>57586</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433383.7589522209</v>
+        <v>433384</v>
       </c>
       <c r="R2" t="n">
-        <v>6205010.714962806</v>
+        <v>6205011</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,7 +780,7 @@
         <v>64029637</v>
       </c>
       <c r="B3" t="n">
-        <v>110539</v>
+        <v>111128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +896,7 @@
         <v>122066207</v>
       </c>
       <c r="B4" t="n">
-        <v>110850</v>
+        <v>111128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30842-2022 artfynd.xlsx
+++ b/artfynd/A 30842-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/34288</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64029637</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122066207</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>